--- a/public/templates/schedule-upload-template.xlsx
+++ b/public/templates/schedule-upload-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KSL_025165\vscode\gms-schedule-app-data\GMS스케줄앱_양식\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KSL-025165\vscode\gms-schedule-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5FC425-6DBC-4171-8EB6-231F1271B2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EAA046-90E2-4F18-B650-DACAF8C8D265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28770" yWindow="16815" windowWidth="28770" windowHeight="15450" xr2:uid="{A5EABDF2-ABAB-4C51-873E-BF56132B24D7}"/>
+    <workbookView xWindow="-21645" yWindow="23670" windowWidth="16215" windowHeight="6765" xr2:uid="{A5EABDF2-ABAB-4C51-873E-BF56132B24D7}"/>
   </bookViews>
   <sheets>
     <sheet name="업로드용" sheetId="1" r:id="rId1"/>
@@ -166,12 +166,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD17B79"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -180,6 +174,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,16 +231,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -550,37 +550,37 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.8984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.8984375" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="8" width="3.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -594,7 +594,7 @@
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -606,10 +606,10 @@
       <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
